--- a/exports/chatbot_evaluation_metrics.xlsx
+++ b/exports/chatbot_evaluation_metrics.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J32"/>
+  <dimension ref="A1:J62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2048,6 +2048,1691 @@
         <v>1</v>
       </c>
     </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-06-29T16:13:35.403229</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>who ranked first</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Candidate 1 from the current ranking list:
+Name: Theju M
+Resume File Name: Theju M.pdf
+Score: 67.0%
+Matched skills: Python, FastAPI, RAG, Docker, Kubernetes, Azure, SQL, AWS, Machine Learning, PyTorch, TensorFlow, CI/CD, Elasticsearch
+Experience match: 100.0%
+Education match: 37.9%</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>0</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="J33" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-07-02T15:12:45.969688</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>why candidate 1 ranked first in ranking list</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ranked first because of the highest matching score against the JD.
+- Candidate: Sara Thomas
+- Matching Score: 46.2%
+- Matched Skills: Python, Azure
+- Missing Required Skills: + years of hands-on Python development., Strong expertise in Python libraries (Pandas, NumPy, Matplotlib, BeautifulSoup)., SQL, Oracle, Agile
+- Experience Alignment: 100.0%
+- Education Alignment: 100.0%
+</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Candidate 1 is ranked at that position because of the current JD match score.
+Candidate: Sara Thomas
+Resume File Name: Sara Thomas.pdf
+Score: 46.2%
+Matched skills: Python, Azure
+Experience match: 100.0%
+Education match: 100.0%</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="J34" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-07-02T15:17:46.287751</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>which candidate ranked first</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ranked first because of the highest matching score against the JD.
+- Candidate: Sara Thomas
+- Matching Score: 46.2%
+- Matched Skills: Python, Azure
+- Missing Required Skills: + years of hands-on Python development., Strong expertise in Python libraries (Pandas, NumPy, Matplotlib, BeautifulSoup)., SQL, Oracle, Agile
+- Experience Alignment: 100.0%
+- Education Alignment: 100.0%
+</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Candidate 1 from the current ranking list:
+Name: Sara Thomas
+Resume File Name: Sara Thomas.pdf
+Score: 46.2%
+Matched skills: Python, Azure
+Experience match: 100.0%
+Education match: 100.0%</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="J35" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-07-02T15:21:40.153367</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>which candidate ranked first</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ranked first because of the highest matching score against the JD.
+- Candidate: Sara Thomas
+- Matching Score: 46.2%
+- Matched Skills: Python, Azure
+- Missing Required Skills: + years of hands-on Python development., Strong expertise in Python libraries (Pandas, NumPy, Matplotlib, BeautifulSoup)., SQL, Oracle, Agile
+- Experience Alignment: 100.0%
+- Education Alignment: 100.0%
+</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Candidate 1 from the current ranking list:
+Name: Sara Thomas
+Resume File Name: Sara Thomas.pdf
+Score: 46.2%
+Matched skills: Python, Azure
+Experience match: 100.0%
+Education match: 100.0%</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>0</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="J36" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-07-02T15:27:34.695919</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>which canidate renked first</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ranked first because of the highest matching score against the JD.
+- Candidate: Sara Thomas
+- Matching Score: 46.2%
+- Matched Skills: Python, Azure
+- Missing Required Skills: + years of hands-on Python development., Strong expertise in Python libraries (Pandas, NumPy, Matplotlib, BeautifulSoup)., SQL, Oracle, Agile
+- Experience Alignment: 100.0%
+- Education Alignment: 100.0%
+</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>No requested skills were found in the question.</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>0</v>
+      </c>
+      <c r="F37" t="n">
+        <v>0</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="J37" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-07-02T15:27:51.136763</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>which canidate ranked first</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ranked first because of the highest matching score against the JD.
+- Candidate: Sara Thomas
+- Matching Score: 46.2%
+- Matched Skills: Python, Azure
+- Missing Required Skills: + years of hands-on Python development., Strong expertise in Python libraries (Pandas, NumPy, Matplotlib, BeautifulSoup)., SQL, Oracle, Agile
+- Experience Alignment: 100.0%
+- Education Alignment: 100.0%
+</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Candidate 1 from the current ranking list:
+Name: Sara Thomas
+Resume File Name: Sara Thomas.pdf
+Score: 46.2%
+Matched skills: Python, Azure
+Experience match: 100.0%
+Education match: 100.0%</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>0</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="J38" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-07-02T15:31:53.737124</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>which candidate ranked first</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ranked first because of the highest matching score against the JD.
+- Candidate: Sara Thomas
+- Matching Score: 46.2%
+- Matched Skills: Python, Azure
+- Missing Required Skills: + years of hands-on Python development., Strong expertise in Python libraries (Pandas, NumPy, Matplotlib, BeautifulSoup)., SQL, Oracle, Agile
+- Experience Alignment: 100.0%
+- Education Alignment: 100.0%
+</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Candidate 1 from the current ranking list:
+Name: Sara Thomas
+Resume File Name: Sara Thomas.pdf
+Score: 46.2%
+Matched skills: Python, Azure
+Experience match: 100.0%
+Education match: 100.0%</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>0</v>
+      </c>
+      <c r="F39" t="n">
+        <v>0</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="J39" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-07-02T15:33:23.739759</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>which candidate ranked first</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ranked first because of the highest matching score against the JD.
+- Candidate: Sara Thomas
+- Matching Score: 46.2%
+- Matched Skills: Python, Azure
+- Missing Required Skills: + years of hands-on Python development., Strong expertise in Python libraries (Pandas, NumPy, Matplotlib, BeautifulSoup)., SQL, Oracle, Agile
+- Experience Alignment: 100.0%
+- Education Alignment: 100.0%
+</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Candidate 1 from the current ranking list:
+Name: Sara Thomas
+Resume File Name: Sara Thomas.pdf
+Score: 46.2%
+Matched skills: Python, Azure
+Experience match: 100.0%
+Education match: 100.0%</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>0</v>
+      </c>
+      <c r="F40" t="n">
+        <v>0</v>
+      </c>
+      <c r="G40" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="J40" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-07-02T15:37:28.088937</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>which candidate ranked first</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ranked first because of the highest matching score against the JD.
+- Candidate: Sara Thomas
+- Matching Score: 46.2%
+- Matched Skills: Python, Azure
+- Missing Required Skills: + years of hands-on Python development., Strong expertise in Python libraries (Pandas, NumPy, Matplotlib, BeautifulSoup)., SQL, Oracle, Agile
+- Experience Alignment: 100.0%
+- Education Alignment: 100.0%
+</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Candidate 1 from the current ranking list:
+Name: Sara Thomas
+Resume File Name: Sara Thomas.pdf
+Score: 46.2%
+Matched skills: Python, Azure
+Experience match: 100.0%
+Education match: 100.0%</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>0</v>
+      </c>
+      <c r="F41" t="n">
+        <v>0</v>
+      </c>
+      <c r="G41" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="J41" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-07-02T15:47:28.619124</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>which candidate ranked first</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ranked first because of the highest matching score against the JD.
+- Candidate: Sara Thomas
+- Matching Score: 46.2%
+- Matched Skills: Python, Azure
+- Missing Required Skills: + years of hands-on Python development., Strong expertise in Python libraries (Pandas, NumPy, Matplotlib, BeautifulSoup)., SQL, Agile, Oracle
+- Experience Alignment: 100.0%
+- Education Alignment: 100.0%
+</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Candidate 1 from the current ranking list:
+Name: Sara Thomas
+Resume File Name: Sara Thomas.pdf
+Score: 46.2%
+Matched skills: Python, Azure
+Experience match: 100.0%
+Education match: 100.0%</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>0</v>
+      </c>
+      <c r="F42" t="n">
+        <v>0</v>
+      </c>
+      <c r="G42" t="n">
+        <v>0</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="J42" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-07-02T15:53:16.062367</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>which candidate ranked first</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ranked first because of the highest matching score against the JD.
+- Candidate: Sara Thomas
+- Matching Score: 46.2%
+- Matched Skills: Python, Azure
+- Missing Required Skills: + years of hands-on Python development., Strong expertise in Python libraries (Pandas, NumPy, Matplotlib, BeautifulSoup)., Oracle, SQL, Agile
+- Experience Alignment: 100.0%
+- Education Alignment: 100.0%
+</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Candidate 1 from the current ranking list:
+Name: Sara Thomas
+Resume File Name: Sara Thomas.pdf
+Score: 46.2%
+Matched skills: Python, Azure
+Experience match: 100.0%
+Education match: 100.0%</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>0</v>
+      </c>
+      <c r="F43" t="n">
+        <v>0</v>
+      </c>
+      <c r="G43" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="J43" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-07-02T15:57:39.679461</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>which candidate  ranked first</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ranked first because of the highest matching score against the JD.
+- Candidate: Sara Thomas
+- Matching Score: 46.2%
+- Matched Skills: Python, Azure
+- Missing Required Skills: + years of hands-on Python development., Strong expertise in Python libraries (Pandas, NumPy, Matplotlib, BeautifulSoup)., Oracle, SQL, Agile
+- Experience Alignment: 100.0%
+- Education Alignment: 100.0%
+</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Candidate 1 from the current ranking list:
+Name: Sara Thomas
+Resume File Name: Sara Thomas.pdf
+Score: 46.2%
+Matched skills: Python, Azure
+Experience match: 100.0%
+Education match: 100.0%</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>0</v>
+      </c>
+      <c r="F44" t="n">
+        <v>0</v>
+      </c>
+      <c r="G44" t="n">
+        <v>0</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="I44" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="J44" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-07-02T16:07:15.549076</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>which candidate ranked first</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ranked first because of the highest matching score against the JD.
+- Candidate: Sara Thomas
+- Matching Score: 46.2%
+- Matched Skills: Python, Azure
+- Missing Required Skills: + years of hands-on Python development., Strong expertise in Python libraries (Pandas, NumPy, Matplotlib, BeautifulSoup)., Oracle, SQL, Agile
+- Experience Alignment: 100.0%
+- Education Alignment: 100.0%
+</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Candidate 1 from the current ranking list:
+Name: Sara Thomas
+Resume File Name: Sara Thomas.pdf
+Score: 46.2%
+Matched skills: Python, Azure
+Experience match: 100.0%
+Education match: 100.0%</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>0</v>
+      </c>
+      <c r="F45" t="n">
+        <v>0</v>
+      </c>
+      <c r="G45" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="I45" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="J45" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-07-02T16:11:34.000300</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>which candidate ranked first</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ranked first because of the highest matching score against the JD.
+- Candidate: Sara Thomas
+- Matching Score: 46.2%
+- Matched Skills: Python, Azure
+- Missing Required Skills: + years of hands-on Python development., Strong expertise in Python libraries (Pandas, NumPy, Matplotlib, BeautifulSoup)., Oracle, SQL, Agile
+- Experience Alignment: 100.0%
+- Education Alignment: 100.0%
+</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Candidate 1 from the current ranking list:
+Name: Sara Thomas
+Resume File Name: Sara Thomas.pdf
+Score: 46.2%
+Matched skills: Python, Azure
+Experience match: 100.0%
+Education match: 100.0%</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>0</v>
+      </c>
+      <c r="F46" t="n">
+        <v>0</v>
+      </c>
+      <c r="G46" t="n">
+        <v>0</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="I46" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="J46" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-07-02T16:14:52.491968</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>which candidate ranked first</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ranked first because of the highest matching score against the JD.
+- Candidate: Sara Thomas
+- Matching Score: 46.2%
+- Matched Skills: Python, Azure
+- Missing Required Skills: + years of hands-on Python development., Strong expertise in Python libraries (Pandas, NumPy, Matplotlib, BeautifulSoup)., Oracle, SQL, Agile
+- Experience Alignment: 100.0%
+- Education Alignment: 100.0%
+</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Candidate 1 from the current ranking list:
+Name: Sara Thomas
+Resume File Name: Sara Thomas.pdf
+Score: 46.2%
+Matched skills: Python, Azure
+Experience match: 100.0%
+Education match: 100.0%</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>0</v>
+      </c>
+      <c r="F47" t="n">
+        <v>0</v>
+      </c>
+      <c r="G47" t="n">
+        <v>0</v>
+      </c>
+      <c r="H47" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="I47" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="J47" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-07-02T16:17:38.605148</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>which candidate ranked first</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ranked first because of the highest matching score against the JD.
+- Candidate: Sara Thomas
+- Matching Score: 46.2%
+- Matched Skills: Python, Azure
+- Missing Required Skills: + years of hands-on Python development., Strong expertise in Python libraries (Pandas, NumPy, Matplotlib, BeautifulSoup)., Oracle, SQL, Agile
+- Experience Alignment: 100.0%
+- Education Alignment: 100.0%
+</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Candidate 1 from the current ranking list:
+Name: Sara Thomas
+Resume File Name: Sara Thomas.pdf
+Score: 46.2%
+Matched skills: Python, Azure
+Experience match: 100.0%
+Education match: 100.0%</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>0</v>
+      </c>
+      <c r="F48" t="n">
+        <v>0</v>
+      </c>
+      <c r="G48" t="n">
+        <v>0</v>
+      </c>
+      <c r="H48" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="I48" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="J48" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-07-02T16:19:25.901180</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>which candidate ranked first</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ranked first because of the highest matching score against the JD.
+- Candidate: Sara Thomas
+- Matching Score: 46.2%
+- Matched Skills: Python, Azure
+- Missing Required Skills: + years of hands-on Python development., Strong expertise in Python libraries (Pandas, NumPy, Matplotlib, BeautifulSoup)., Oracle, SQL, Agile
+- Experience Alignment: 100.0%
+- Education Alignment: 100.0%
+</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Candidate 1 from the current ranking list:
+Name: Sara Thomas
+Resume File Name: Sara Thomas.pdf
+Score: 46.2%
+Matched skills: Python, Azure
+Experience match: 100.0%
+Education match: 100.0%</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>0</v>
+      </c>
+      <c r="F49" t="n">
+        <v>0</v>
+      </c>
+      <c r="G49" t="n">
+        <v>0</v>
+      </c>
+      <c r="H49" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="I49" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="J49" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-07-02T16:20:56.609800</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>which candidate ranked first</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ranked first because of the highest matching score against the JD.
+- Candidate: Sara Thomas
+- Matching Score: 46.2%
+- Matched Skills: Python, Azure
+- Missing Required Skills: + years of hands-on Python development., Strong expertise in Python libraries (Pandas, NumPy, Matplotlib, BeautifulSoup)., Oracle, SQL, Agile
+- Experience Alignment: 100.0%
+- Education Alignment: 100.0%
+</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Candidate 1 from the current ranking list:
+Name: Sara Thomas
+Resume File Name: Sara Thomas.pdf
+Score: 46.2%
+Matched skills: Python, Azure
+Experience match: 100.0%
+Education match: 100.0%</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>0</v>
+      </c>
+      <c r="F50" t="n">
+        <v>0</v>
+      </c>
+      <c r="G50" t="n">
+        <v>0</v>
+      </c>
+      <c r="H50" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="I50" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="J50" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-07-02T16:22:32.731382</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>which candidate ranked first</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ranked first because of the highest matching score against the JD.
+- Candidate: Sara Thomas
+- Matching Score: 46.2%
+- Matched Skills: Python, Azure
+- Missing Required Skills: + years of hands-on Python development., Strong expertise in Python libraries (Pandas, NumPy, Matplotlib, BeautifulSoup)., Oracle, SQL, Agile
+- Experience Alignment: 100.0%
+- Education Alignment: 100.0%
+</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Candidate 1 from the current ranking list:
+Name: Sara Thomas
+Resume File Name: Sara Thomas.pdf
+Score: 46.2%
+Matched skills: Python, Azure
+Experience match: 100.0%
+Education match: 100.0%</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>0</v>
+      </c>
+      <c r="F51" t="n">
+        <v>0</v>
+      </c>
+      <c r="G51" t="n">
+        <v>0</v>
+      </c>
+      <c r="H51" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="I51" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="J51" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-07-02T16:22:42.393633</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>which candidate ranked first</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ranked first because of the highest matching score against the JD.
+- Candidate: Sara Thomas
+- Matching Score: 46.2%
+- Matched Skills: Python, Azure
+- Missing Required Skills: + years of hands-on Python development., Strong expertise in Python libraries (Pandas, NumPy, Matplotlib, BeautifulSoup)., Oracle, SQL, Agile
+- Experience Alignment: 100.0%
+- Education Alignment: 100.0%
+</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Candidate 1 from the current ranking list:
+Name: Sara Thomas
+Resume File Name: Sara Thomas.pdf
+Score: 46.2%
+Matched skills: Python, Azure
+Experience match: 100.0%
+Education match: 100.0%</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>0</v>
+      </c>
+      <c r="F52" t="n">
+        <v>0</v>
+      </c>
+      <c r="G52" t="n">
+        <v>0</v>
+      </c>
+      <c r="H52" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="I52" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="J52" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026-07-02T16:22:57.738744</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>which candidate ranked secound</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr"/>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>No candidates found with secound evidence.</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>0</v>
+      </c>
+      <c r="F53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G53" t="n">
+        <v>0</v>
+      </c>
+      <c r="H53" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I53" t="n">
+        <v>0</v>
+      </c>
+      <c r="J53" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026-07-02T16:23:09.492545</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>which candidate ranked second</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr"/>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Candidate 2 from the current ranking list:
+Name: Rahul Mehta
+Resume File Name: Rahul Mehta.pdf
+Score: 45.1%
+Matched skills: Azure
+Experience match: 100.0%
+Education match: 100.0%</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>0</v>
+      </c>
+      <c r="F54" t="n">
+        <v>0</v>
+      </c>
+      <c r="G54" t="n">
+        <v>0</v>
+      </c>
+      <c r="H54" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="I54" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="J54" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-07-02T16:26:18.890584</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>compare candidate 1 and candidate 2</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Comparison generated from ranking data.
+Sara Thomas:
+- Overall Score: 46.2%
+- Required Skills Matched: Python, Azure
+- Missing Required Skills: + years of hands-on Python development., Strong expertise in Python libraries (Pandas, NumPy, Matplotlib, BeautifulSoup)., Oracle, SQL, Agile
+- Experience: pipelines, and improving system reliability across AWS and Azure environments. Passionate about Infrastructure as Code and reducing operational toil.
+- Education: B.Tech in Information Technology, Cochin University of Science and Technology | 2015 – 2019
+- Rank Position: 1
+Rahul Mehta:
+- Overall Score: 45.1%
+- Required Skills Matched: Azure
+- Missing Required Skills: Python, + years of hands-on Python development., Strong expertise in Python libraries (Pandas, NumPy, Matplotlib, BeautifulSoup)., Oracle, SQL, Agile
+- Experience: applications. Strong background in React, Node.js, and cloud deployment, with a focus on clean architecture and
+- Education: B.Tech in Computer Science and Engineering, Vellore Institute of Technology | 2016 – 2020
+- Rank Position: 2
+</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Candidate 1:
+- Name: Sara Thomas
+- Resume File Name: Sara Thomas.pdf
+- Match Score: 46.2%
+- Skills: Python, Azure
+- Experience Summary: pipelines, and improving system reliability across AWS and Azure environments. Passionate about Infrastructure as Code and reducing operational toil.
+- Education: B.Tech in Information Technology, Cochin University of Science and Technology 2015 – 2019
+Candidate 2:
+- Name: Rahul Mehta
+- Resume File Name: Rahul Mehta.pdf
+- Match Score: 45.1%
+- Skills: Azure
+- Experience Summary: applications. Strong background in React, Node.js, and cloud deployment, with a focus on clean architecture and
+- Education: B.Tech in Computer Science and Engineering, Vellore Institute of Technology 2016 – 2020
+Key Differences:
+- Skills Difference: Candidate 1 only: Python
+- Experience Difference: Both candidates have the same experience alignment score.
+- Education Difference: Candidate 1: B.Tech in Information Technology, Cochin University of Science and Technology 2015 – 2019; Candidate 2: B.Tech in Computer Science and Engineering, Vellore Institute of Technology 2016 – 2020
+- Match Score Difference: Candidate 1 is higher by 1.1 percentage points.</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>0</v>
+      </c>
+      <c r="F55" t="n">
+        <v>0</v>
+      </c>
+      <c r="G55" t="n">
+        <v>0</v>
+      </c>
+      <c r="H55" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="I55" t="n">
+        <v>1</v>
+      </c>
+      <c r="J55" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2026-07-02T16:28:27.081978</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>compare candidate 1 and candidate 2</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Comparison generated from ranking data.
+Sara Thomas:
+- Overall Score: 46.2%
+- Required Skills Matched: Python, Azure
+- Missing Required Skills: + years of hands-on Python development., Strong expertise in Python libraries (Pandas, NumPy, Matplotlib, BeautifulSoup)., Oracle, SQL, Agile
+- Experience: pipelines, and improving system reliability across AWS and Azure environments. Passionate about Infrastructure as Code and reducing operational toil.
+- Education: B.Tech in Information Technology, Cochin University of Science and Technology | 2015 – 2019
+- Rank Position: 1
+Rahul Mehta:
+- Overall Score: 45.1%
+- Required Skills Matched: Azure
+- Missing Required Skills: Python, + years of hands-on Python development., Strong expertise in Python libraries (Pandas, NumPy, Matplotlib, BeautifulSoup)., Oracle, SQL, Agile
+- Experience: applications. Strong background in React, Node.js, and cloud deployment, with a focus on clean architecture and
+- Education: B.Tech in Computer Science and Engineering, Vellore Institute of Technology | 2016 – 2020
+- Rank Position: 2
+</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Candidate 1:
+- Name: Sara Thomas
+- Resume File Name: Sara Thomas.pdf
+- Match Score: 46.2%
+- Skills: Python, Azure
+- Experience Summary: pipelines, and improving system reliability across AWS and Azure environments. Passionate about Infrastructure as Code and reducing operational toil.
+- Education: B.Tech in Information Technology, Cochin University of Science and Technology 2015 – 2019
+Candidate 2:
+- Name: Rahul Mehta
+- Resume File Name: Rahul Mehta.pdf
+- Match Score: 45.1%
+- Skills: Azure
+- Experience Summary: applications. Strong background in React, Node.js, and cloud deployment, with a focus on clean architecture and
+- Education: B.Tech in Computer Science and Engineering, Vellore Institute of Technology 2016 – 2020
+Key Differences:
+- Skills Difference: Candidate 1 only: Python
+- Experience Difference: Both candidates have the same experience alignment score.
+- Education Difference: Candidate 1: B.Tech in Information Technology, Cochin University of Science and Technology 2015 – 2019; Candidate 2: B.Tech in Computer Science and Engineering, Vellore Institute of Technology 2016 – 2020
+- Match Score Difference: Candidate 1 is higher by 1.1 percentage points.</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>0</v>
+      </c>
+      <c r="F56" t="n">
+        <v>0</v>
+      </c>
+      <c r="G56" t="n">
+        <v>0</v>
+      </c>
+      <c r="H56" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="I56" t="n">
+        <v>1</v>
+      </c>
+      <c r="J56" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-07-02T16:28:35.063197</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>compare candidate 1 and candidate 2</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Comparison generated from ranking data.
+Sara Thomas:
+- Overall Score: 46.2%
+- Required Skills Matched: Python, Azure
+- Missing Required Skills: + years of hands-on Python development., Strong expertise in Python libraries (Pandas, NumPy, Matplotlib, BeautifulSoup)., Oracle, SQL, Agile
+- Experience: pipelines, and improving system reliability across AWS and Azure environments. Passionate about Infrastructure as Code and reducing operational toil.
+- Education: B.Tech in Information Technology, Cochin University of Science and Technology | 2015 – 2019
+- Rank Position: 1
+Rahul Mehta:
+- Overall Score: 45.1%
+- Required Skills Matched: Azure
+- Missing Required Skills: Python, + years of hands-on Python development., Strong expertise in Python libraries (Pandas, NumPy, Matplotlib, BeautifulSoup)., Oracle, SQL, Agile
+- Experience: applications. Strong background in React, Node.js, and cloud deployment, with a focus on clean architecture and
+- Education: B.Tech in Computer Science and Engineering, Vellore Institute of Technology | 2016 – 2020
+- Rank Position: 2
+</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Candidate 1:
+- Name: Sara Thomas
+- Resume File Name: Sara Thomas.pdf
+- Match Score: 46.2%
+- Skills: Python, Azure
+- Experience Summary: pipelines, and improving system reliability across AWS and Azure environments. Passionate about Infrastructure as Code and reducing operational toil.
+- Education: B.Tech in Information Technology, Cochin University of Science and Technology 2015 – 2019
+Candidate 2:
+- Name: Rahul Mehta
+- Resume File Name: Rahul Mehta.pdf
+- Match Score: 45.1%
+- Skills: Azure
+- Experience Summary: applications. Strong background in React, Node.js, and cloud deployment, with a focus on clean architecture and
+- Education: B.Tech in Computer Science and Engineering, Vellore Institute of Technology 2016 – 2020
+Key Differences:
+- Skills Difference: Candidate 1 only: Python
+- Experience Difference: Both candidates have the same experience alignment score.
+- Education Difference: Candidate 1: B.Tech in Information Technology, Cochin University of Science and Technology 2015 – 2019; Candidate 2: B.Tech in Computer Science and Engineering, Vellore Institute of Technology 2016 – 2020
+- Match Score Difference: Candidate 1 is higher by 1.1 percentage points.</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>0</v>
+      </c>
+      <c r="F57" t="n">
+        <v>0</v>
+      </c>
+      <c r="G57" t="n">
+        <v>0</v>
+      </c>
+      <c r="H57" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="I57" t="n">
+        <v>1</v>
+      </c>
+      <c r="J57" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-07-02T16:31:16.294713</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>compare candidate 1 and candidate 2</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Comparison generated from ranking data.
+Sara Thomas:
+- Overall Score: 46.2%
+- Required Skills Matched: Python, Azure
+- Missing Required Skills: + years of hands-on Python development., Strong expertise in Python libraries (Pandas, NumPy, Matplotlib, BeautifulSoup)., Oracle, SQL, Agile
+- Experience: pipelines, and improving system reliability across AWS and Azure environments. Passionate about Infrastructure as Code and reducing operational toil.
+- Education: B.Tech in Information Technology, Cochin University of Science and Technology | 2015 – 2019
+- Rank Position: 1
+Rahul Mehta:
+- Overall Score: 45.1%
+- Required Skills Matched: Azure
+- Missing Required Skills: Python, + years of hands-on Python development., Strong expertise in Python libraries (Pandas, NumPy, Matplotlib, BeautifulSoup)., Oracle, SQL, Agile
+- Experience: applications. Strong background in React, Node.js, and cloud deployment, with a focus on clean architecture and
+- Education: B.Tech in Computer Science and Engineering, Vellore Institute of Technology | 2016 – 2020
+- Rank Position: 2
+</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Candidate 1:
+- Name: Sara Thomas
+- Resume File Name: Sara Thomas.pdf
+- Match Score: 46.2%
+- Skills: Python, Azure
+- Experience Summary: pipelines, and improving system reliability across AWS and Azure environments. Passionate about Infrastructure as Code and reducing operational toil.
+- Education: B.Tech in Information Technology, Cochin University of Science and Technology 2015 – 2019
+Candidate 2:
+- Name: Rahul Mehta
+- Resume File Name: Rahul Mehta.pdf
+- Match Score: 45.1%
+- Skills: Azure
+- Experience Summary: applications. Strong background in React, Node.js, and cloud deployment, with a focus on clean architecture and
+- Education: B.Tech in Computer Science and Engineering, Vellore Institute of Technology 2016 – 2020
+Key Differences:
+- Skills Difference: Candidate 1 only: Python
+- Experience Difference: Both candidates have the same experience alignment score.
+- Education Difference: Candidate 1: B.Tech in Information Technology, Cochin University of Science and Technology 2015 – 2019; Candidate 2: B.Tech in Computer Science and Engineering, Vellore Institute of Technology 2016 – 2020
+- Match Score Difference: Candidate 1 is higher by 1.1 percentage points.</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>0</v>
+      </c>
+      <c r="F58" t="n">
+        <v>0</v>
+      </c>
+      <c r="G58" t="n">
+        <v>0</v>
+      </c>
+      <c r="H58" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="I58" t="n">
+        <v>1</v>
+      </c>
+      <c r="J58" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2026-07-02T16:51:49.780368</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">compare candidate 1 and candidate 2
+</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Comparison generated from ranking data.
+Sara Thomas:
+- Overall Score: 46.2%
+- Required Skills Matched: Python, Azure
+- Missing Required Skills: + years of hands-on Python development., Strong expertise in Python libraries (Pandas, NumPy, Matplotlib, BeautifulSoup)., Oracle, SQL, Agile
+- Experience: pipelines, and improving system reliability across AWS and Azure environments. Passionate about Infrastructure as Code and reducing operational toil.
+- Education: B.Tech in Information Technology, Cochin University of Science and Technology | 2015 – 2019
+- Rank Position: 1
+Rahul Mehta:
+- Overall Score: 45.1%
+- Required Skills Matched: Azure
+- Missing Required Skills: Python, + years of hands-on Python development., Strong expertise in Python libraries (Pandas, NumPy, Matplotlib, BeautifulSoup)., Oracle, SQL, Agile
+- Experience: applications. Strong background in React, Node.js, and cloud deployment, with a focus on clean architecture and
+- Education: B.Tech in Computer Science and Engineering, Vellore Institute of Technology | 2016 – 2020
+- Rank Position: 2
+</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Candidate 1:
+- Name: Sara Thomas
+- Resume File Name: Sara Thomas.pdf
+- Match Score: 46.2%
+- Skills: Python, Azure
+- Experience Summary: pipelines, and improving system reliability across AWS and Azure environments. Passionate about Infrastructure as Code and reducing operational toil.
+- Education: B.Tech in Information Technology, Cochin University of Science and Technology 2015 – 2019
+Candidate 2:
+- Name: Rahul Mehta
+- Resume File Name: Rahul Mehta.pdf
+- Match Score: 45.1%
+- Skills: Azure
+- Experience Summary: applications. Strong background in React, Node.js, and cloud deployment, with a focus on clean architecture and
+- Education: B.Tech in Computer Science and Engineering, Vellore Institute of Technology 2016 – 2020
+Key Differences:
+- Skills Difference: Candidate 1 only: Python
+- Experience Difference: Both candidates have the same experience alignment score.
+- Education Difference: Candidate 1: B.Tech in Information Technology, Cochin University of Science and Technology 2015 – 2019; Candidate 2: B.Tech in Computer Science and Engineering, Vellore Institute of Technology 2016 – 2020
+- Match Score Difference: Candidate 1 is higher by 1.1 percentage points.</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>0</v>
+      </c>
+      <c r="F59" t="n">
+        <v>0</v>
+      </c>
+      <c r="G59" t="n">
+        <v>0</v>
+      </c>
+      <c r="H59" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="I59" t="n">
+        <v>1</v>
+      </c>
+      <c r="J59" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2026-07-02T16:53:21.651219</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">compare candidate 1 and candidate 2
+</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Comparison generated from ranking data.
+Sara Thomas:
+- Overall Score: 46.2%
+- Required Skills Matched: Python, Azure
+- Missing Required Skills: + years of hands-on Python development., Strong expertise in Python libraries (Pandas, NumPy, Matplotlib, BeautifulSoup)., Oracle, SQL, Agile
+- Experience: pipelines, and improving system reliability across AWS and Azure environments. Passionate about Infrastructure as Code and reducing operational toil.
+- Education: B.Tech in Information Technology, Cochin University of Science and Technology | 2015 – 2019
+- Rank Position: 1
+Rahul Mehta:
+- Overall Score: 45.1%
+- Required Skills Matched: Azure
+- Missing Required Skills: Python, + years of hands-on Python development., Strong expertise in Python libraries (Pandas, NumPy, Matplotlib, BeautifulSoup)., Oracle, SQL, Agile
+- Experience: applications. Strong background in React, Node.js, and cloud deployment, with a focus on clean architecture and
+- Education: B.Tech in Computer Science and Engineering, Vellore Institute of Technology | 2016 – 2020
+- Rank Position: 2
+</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Candidate 1:
+- Name: Sara Thomas
+- Resume File Name: Sara Thomas.pdf
+- Match Score: 46.2%
+- Skills: Python, Azure
+- Experience Summary: pipelines, and improving system reliability across AWS and Azure environments. Passionate about Infrastructure as Code and reducing operational toil.
+- Education: B.Tech in Information Technology, Cochin University of Science and Technology 2015 – 2019
+Candidate 2:
+- Name: Rahul Mehta
+- Resume File Name: Rahul Mehta.pdf
+- Match Score: 45.1%
+- Skills: Azure
+- Experience Summary: applications. Strong background in React, Node.js, and cloud deployment, with a focus on clean architecture and
+- Education: B.Tech in Computer Science and Engineering, Vellore Institute of Technology 2016 – 2020
+Key Differences:
+- Skills Difference: Candidate 1 only: Python
+- Experience Difference: Both candidates have the same experience alignment score.
+- Education Difference: Candidate 1: B.Tech in Information Technology, Cochin University of Science and Technology 2015 – 2019; Candidate 2: B.Tech in Computer Science and Engineering, Vellore Institute of Technology 2016 – 2020
+- Match Score Difference: Candidate 1 is higher by 1.1 percentage points.</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>0</v>
+      </c>
+      <c r="F60" t="n">
+        <v>0</v>
+      </c>
+      <c r="G60" t="n">
+        <v>0</v>
+      </c>
+      <c r="H60" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="I60" t="n">
+        <v>1</v>
+      </c>
+      <c r="J60" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2026-07-03T12:16:19.414717</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>compare candidate 1 and candidate 2</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Comparison generated from ranking data.
+Sara Thomas:
+- Overall Score: 46.2%
+- Required Skills Matched: Python, Azure
+- Missing Required Skills: + years of hands-on Python development., Strong expertise in Python libraries (Pandas, NumPy, Matplotlib, BeautifulSoup)., Agile, SQL, Oracle
+- Experience: pipelines, and improving system reliability across AWS and Azure environments. Passionate about Infrastructure as Code and reducing operational toil.
+- Education: B.Tech in Information Technology, Cochin University of Science and Technology | 2015 – 2019
+- Rank Position: 1
+Rahul Mehta:
+- Overall Score: 45.1%
+- Required Skills Matched: Azure
+- Missing Required Skills: Python, + years of hands-on Python development., Strong expertise in Python libraries (Pandas, NumPy, Matplotlib, BeautifulSoup)., Agile, SQL, Oracle
+- Experience: applications. Strong background in React, Node.js, and cloud deployment, with a focus on clean architecture and
+- Education: B.Tech in Computer Science and Engineering, Vellore Institute of Technology | 2016 – 2020
+- Rank Position: 2
+</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Candidate 1:
+- Name: Sara Thomas (Sara Thomas.pdf)
+- Match Score: 46.2%
+- Skills: Python, Azure
+- Experience Summary: pipelines, and improving system reliability across AWS and Azure environments. Passionate about Infrastructure as Code and reducing operational toil.
+- Education: B.Tech in Information Technology, Cochin University of Science and Technology 2015 – 2019
+Candidate 2:
+- Name: Rahul Mehta (Rahul Mehta.pdf)
+- Match Score: 45.1%
+- Skills: Azure
+- Experience Summary: applications. Strong background in React, Node.js, and cloud deployment, with a focus on clean architecture and
+- Education: B.Tech in Computer Science and Engineering, Vellore Institute of Technology 2016 – 2020
+Key Differences:
+- Skills Difference: Candidate 1 only: Python
+- Experience Difference: Both candidates have the same experience alignment score.
+- Education Difference: Candidate 1: B.Tech in Information Technology, Cochin University of Science and Technology 2015 – 2019; Candidate 2: B.Tech in Computer Science and Engineering, Vellore Institute of Technology 2016 – 2020
+- Match Score Difference: Candidate 1 is higher by 1.1 percentage points.</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>0</v>
+      </c>
+      <c r="F61" t="n">
+        <v>0</v>
+      </c>
+      <c r="G61" t="n">
+        <v>0</v>
+      </c>
+      <c r="H61" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="I61" t="n">
+        <v>1</v>
+      </c>
+      <c r="J61" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-07-03T12:16:56.970340</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>why candidate 5 ranked</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ranked first because of the highest matching score against the JD.
+- Candidate: Sara Thomas
+- Matching Score: 46.2%
+- Matched Skills: Python, Azure
+- Missing Required Skills: + years of hands-on Python development., Strong expertise in Python libraries (Pandas, NumPy, Matplotlib, BeautifulSoup)., Agile, SQL, Oracle
+- Experience Alignment: 100.0%
+- Education Alignment: 100.0%
+</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Candidate 5 is ranked at that position because of the current JD match score.
+Candidate: Priya Nair
+Resume File Name: Priya Nair.pdf
+Score: 21.1%
+Matched skills: None recorded
+Experience match: 80.0%
+Education match: 0.0%</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>0</v>
+      </c>
+      <c r="F62" t="n">
+        <v>0</v>
+      </c>
+      <c r="G62" t="n">
+        <v>0</v>
+      </c>
+      <c r="H62" t="n">
+        <v>1</v>
+      </c>
+      <c r="I62" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J62" t="b">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
